--- a/Test/Test Case.xlsx
+++ b/Test/Test Case.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Embedded_work\PROJECTS\PIR_Security_Node\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C5A341B-2D82-4D44-8782-C3D36B28AA2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528BE5BF-3452-4325-9565-D2656CB9258F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3048" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
   <si>
     <t>Test ID</t>
   </si>
@@ -85,9 +85,6 @@
   </si>
   <si>
     <t>System disarmed</t>
-  </si>
-  <si>
-    <t>FAIL</t>
   </si>
 </sst>
 </file>
@@ -480,7 +477,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -497,7 +494,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -511,7 +508,7 @@
         <v>19</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
